--- a/K리그 1_2026.xlsx
+++ b/K리그 1_2026.xlsx
@@ -422,180 +422,210 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q97"/>
+  <dimension ref="A1:T109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LEAGUE</t>
+          <t>리그</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>SEASON</t>
+          <t>시즌</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ROUND</t>
+          <t>라운드</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>날짜</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>시간</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>HOME_TEAM</t>
+          <t>홈</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>HOME_RANK</t>
+          <t>홈순위</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>HOME_SCORE</t>
+          <t>홈점수</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>AWAY_SCORE</t>
+          <t>원정점수</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>AWAY_TEAM</t>
+          <t>원정순위</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>AWAY_RANK</t>
+          <t>원정</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>AVERAGE_W</t>
+          <t>승</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>AVERAGE_D</t>
+          <t>무</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>AVERAGE_L</t>
+          <t>패</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>기본_W</t>
+          <t>오버</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>기본_D</t>
+          <t>오버라인</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>기본_L</t>
+          <t>언더</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>핸디캡홈</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>핸디캡라인</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>핸디캡원정</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>K리그 1</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>02.28</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>강원</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>3.1</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>3.10</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>3.00</t>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -627,62 +657,77 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -734,42 +779,57 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>포항</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
         </is>
       </c>
     </row>
@@ -821,17 +881,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>부천</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -841,22 +901,37 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.5/3</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1/1.5</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
         </is>
       </c>
     </row>
@@ -908,14 +983,14 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>광주</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>2.25</t>
@@ -923,27 +998,42 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -995,14 +1085,14 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>안양</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
           <t>1.75</t>
@@ -1010,27 +1100,42 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -1062,62 +1167,77 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>광주</t>
+          <t>부천</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
         </is>
       </c>
     </row>
@@ -1149,62 +1269,77 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>부천</t>
+          <t>광주</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -1256,14 +1391,14 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>전북</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -1271,7 +1406,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1281,17 +1416,32 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
         </is>
       </c>
     </row>
@@ -1343,42 +1493,57 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>제주</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
         </is>
       </c>
     </row>
@@ -1430,14 +1595,14 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>강원</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -1445,7 +1610,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1455,17 +1620,32 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -1517,42 +1697,57 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>서울</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
         </is>
       </c>
     </row>
@@ -1604,14 +1799,14 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>전북</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>3.25</t>
@@ -1619,7 +1814,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1629,17 +1824,32 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
         </is>
       </c>
     </row>
@@ -1691,42 +1901,57 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>김천</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
         </is>
       </c>
     </row>
@@ -1778,17 +2003,17 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>울산</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1803,17 +2028,32 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
         </is>
       </c>
     </row>
@@ -1865,22 +2105,22 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>서울</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1890,17 +2130,32 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -1952,42 +2207,57 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>안양</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
         </is>
       </c>
     </row>
@@ -2039,42 +2309,57 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>인천</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
         </is>
       </c>
     </row>
@@ -2126,42 +2411,57 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>광주</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
         </is>
       </c>
     </row>
@@ -2213,17 +2513,17 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
           <t>강원</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -2238,17 +2538,32 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -2300,14 +2615,14 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>대전</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
           <t>2.35</t>
@@ -2315,7 +2630,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2325,17 +2640,32 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
         </is>
       </c>
     </row>
@@ -2367,62 +2697,77 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>안양</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
         </is>
       </c>
     </row>
@@ -2454,62 +2799,77 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>안양</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -2561,22 +2921,22 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>서울</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2586,17 +2946,32 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
         </is>
       </c>
     </row>
@@ -2648,42 +3023,57 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
           <t>전북</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
         </is>
       </c>
     </row>
@@ -2735,14 +3125,14 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
           <t>광주</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
           <t>1.65</t>
@@ -2750,7 +3140,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2760,17 +3150,32 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>0.5/1</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
         </is>
       </c>
     </row>
@@ -2822,14 +3227,14 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
           <t>김천</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
           <t>2.05</t>
@@ -2842,22 +3247,37 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -2889,62 +3309,77 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>안양</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
         </is>
       </c>
     </row>
@@ -2976,17 +3411,17 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>안양</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2996,42 +3431,57 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
         </is>
       </c>
     </row>
@@ -3083,42 +3533,57 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
           <t>부천</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>0.5/1</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
         </is>
       </c>
     </row>
@@ -3150,17 +3615,17 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3170,42 +3635,57 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>부천</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -3237,17 +3717,17 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -3257,42 +3737,57 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>부천</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -3344,14 +3839,14 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
           <t>광주</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
           <t>1.67</t>
@@ -3364,22 +3859,37 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>0.5/1</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -3431,22 +3941,22 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
           <t>대전</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3456,17 +3966,32 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
         </is>
       </c>
     </row>
@@ -3518,42 +4043,57 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
           <t>서울</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
         </is>
       </c>
     </row>
@@ -3605,14 +4145,14 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
           <t>김천</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
           <t>2.15</t>
@@ -3620,27 +4160,42 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -3672,62 +4227,77 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>포항</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
         </is>
       </c>
     </row>
@@ -3759,62 +4329,77 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>포항</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
           <t>1.90</t>
         </is>
       </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
-          <t>3.90</t>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -3866,22 +4451,22 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
           <t>부천</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3891,17 +4476,32 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
         </is>
       </c>
     </row>
@@ -3953,42 +4553,57 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
           <t>울산</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -4040,22 +4655,22 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
           <t>강원</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -4065,17 +4680,32 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
         </is>
       </c>
     </row>
@@ -4127,14 +4757,14 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
           <t>안양</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
           <t>2.15</t>
@@ -4147,22 +4777,37 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
         </is>
       </c>
     </row>
@@ -4214,42 +4859,57 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
           <t>전북</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
         </is>
       </c>
     </row>
@@ -4301,17 +4961,17 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
           <t>대전</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -4321,22 +4981,37 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
           <t>1.80</t>
         </is>
       </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>4.20</t>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -4388,42 +5063,57 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
           <t>인천</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
         </is>
       </c>
     </row>
@@ -4475,17 +5165,17 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
           <t>김천</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -4500,17 +5190,32 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
         </is>
       </c>
     </row>
@@ -4562,42 +5267,57 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
           <t>광주</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
         </is>
       </c>
     </row>
@@ -4649,14 +5369,14 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
           <t>안양</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
           <t>2.05</t>
@@ -4664,27 +5384,42 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -4736,14 +5471,14 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
           <t>강원</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
           <t>2.88</t>
@@ -4751,7 +5486,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4761,17 +5496,32 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
         </is>
       </c>
     </row>
@@ -4803,62 +5553,77 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>서울</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>부천</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -4890,62 +5655,77 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>전북</t>
+          <t>서울</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>부천</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>0.5/1</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -4977,17 +5757,17 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>안양</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -4997,42 +5777,57 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
         </is>
       </c>
     </row>
@@ -5064,62 +5859,77 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>안양</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>제주</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>0.5/1</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -5171,14 +5981,14 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
           <t>광주</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
           <t>1.55</t>
@@ -5186,27 +5996,42 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
         </is>
       </c>
     </row>
@@ -5258,14 +6083,14 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
           <t>서울</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
           <t>2.55</t>
@@ -5273,27 +6098,42 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
         </is>
       </c>
     </row>
@@ -5345,14 +6185,14 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
           <t>김천</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
           <t>2.75</t>
@@ -5360,7 +6200,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -5370,17 +6210,32 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
         </is>
       </c>
     </row>
@@ -5432,14 +6287,14 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
           <t>제주</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
           <t>1.95</t>
@@ -5447,27 +6302,42 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -5519,14 +6389,14 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
           <t>포항</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
           <t>1.95</t>
@@ -5539,22 +6409,37 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -5606,42 +6491,57 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
           <t>안양</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
         </is>
       </c>
     </row>
@@ -5693,42 +6593,57 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
           <t>대전</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
         </is>
       </c>
     </row>
@@ -5780,14 +6695,14 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
           <t>김천</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
           <t>1.73</t>
@@ -5795,7 +6710,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5805,17 +6720,32 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>0.5/1</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -5867,42 +6797,57 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
           <t>포항</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
         </is>
       </c>
     </row>
@@ -5954,14 +6899,14 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
           <t>강원</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
           <t>2.88</t>
@@ -5969,27 +6914,42 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
         </is>
       </c>
     </row>
@@ -6041,40 +7001,55 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
           <t>전북</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr">
         <is>
           <t>1.80</t>
         </is>
@@ -6108,12 +7083,12 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>광주</t>
+          <t>안양</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -6123,45 +7098,60 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>부천</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr">
         <is>
           <t>1.80</t>
         </is>
@@ -6195,12 +7185,12 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>안양</t>
+          <t>광주</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -6210,47 +7200,62 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>부천</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -6302,42 +7307,57 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
           <t>제주</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
         </is>
       </c>
     </row>
@@ -6389,14 +7409,14 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
           <t>광주</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
           <t>1.33</t>
@@ -6409,22 +7429,37 @@
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>1/1.5</t>
+        </is>
+      </c>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -6456,62 +7491,77 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>포항</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -6543,12 +7593,12 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>김천</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -6558,47 +7608,62 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>포항</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>울산</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="O71" s="2" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="P71" s="2" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
       <c r="Q71" s="2" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
         </is>
       </c>
     </row>
@@ -6630,62 +7695,77 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>김천</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>인천</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="O72" s="2" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="P72" s="2" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="Q72" s="2" t="inlineStr">
-        <is>
-          <t>3.20</t>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -6737,22 +7817,22 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
           <t>안양</t>
         </is>
       </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -6762,17 +7842,32 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>0.5/1</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -6824,14 +7919,14 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
           <t>서울</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
           <t>3.75</t>
@@ -6839,27 +7934,42 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
         </is>
       </c>
     </row>
@@ -6891,12 +8001,12 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>광주</t>
+          <t>김천</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6906,47 +8016,62 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>인천</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
         </is>
       </c>
     </row>
@@ -6978,12 +8103,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>김천</t>
+          <t>광주</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6993,47 +8118,62 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>인천</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>-1/1.5</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
         </is>
       </c>
     </row>
@@ -7085,14 +8225,14 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
           <t>포항</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
           <t>2.15</t>
@@ -7100,7 +8240,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -7110,17 +8250,32 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="S77" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T77" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
         </is>
       </c>
     </row>
@@ -7172,14 +8327,14 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
           <t>부천</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
           <t>1.67</t>
@@ -7187,7 +8342,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -7197,17 +8352,32 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>0.5/1</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -7259,14 +8429,14 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
           <t>전북</t>
         </is>
       </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
           <t>3.25</t>
@@ -7274,7 +8444,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -7284,17 +8454,32 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
         </is>
       </c>
     </row>
@@ -7346,42 +8531,57 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
           <t>대전</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="S80" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T80" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
         </is>
       </c>
     </row>
@@ -7433,22 +8633,22 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
           <t>서울</t>
         </is>
       </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -7458,17 +8658,32 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="S81" s="2" t="inlineStr">
+        <is>
+          <t>-1/1.5</t>
+        </is>
+      </c>
+      <c r="T81" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
         </is>
       </c>
     </row>
@@ -7520,14 +8735,14 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
           <t>포항</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
           <t>2.45</t>
@@ -7535,7 +8750,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -7545,17 +8760,32 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="S82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
         </is>
       </c>
     </row>
@@ -7587,62 +8817,77 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>부천</t>
+          <t>안양</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>김천</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="S83" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>전북</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="P83" s="2" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="Q83" s="2" t="inlineStr">
-        <is>
-          <t>1.75</t>
+      <c r="T83" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
         </is>
       </c>
     </row>
@@ -7674,62 +8919,77 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>안양</t>
+          <t>부천</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>김천</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>전북</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="S84" s="2" t="inlineStr">
+        <is>
+          <t>-0.5/1</t>
+        </is>
+      </c>
+      <c r="T84" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
         </is>
       </c>
     </row>
@@ -7781,14 +9041,14 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
           <t>제주</t>
         </is>
       </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
           <t>1.85</t>
@@ -7796,12 +9056,12 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
@@ -7811,12 +9071,27 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S85" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T85" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -7868,42 +9143,57 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
           <t>서울</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="S86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -7955,14 +9245,14 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
           <t>광주</t>
         </is>
       </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
           <t>1.48</t>
@@ -7975,22 +9265,37 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T87" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -8042,14 +9347,14 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
           <t>안양</t>
         </is>
       </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
           <t>2.45</t>
@@ -8057,7 +9362,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -8067,17 +9372,32 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="S88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T88" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
         </is>
       </c>
     </row>
@@ -8129,14 +9449,14 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
           <t>김천</t>
         </is>
       </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
           <t>1.67</t>
@@ -8144,7 +9464,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -8154,17 +9474,32 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>0.5/1</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -8196,12 +9531,12 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>강원</t>
+          <t>부천</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -8216,42 +9551,57 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>포항</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="S90" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T90" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
         </is>
       </c>
     </row>
@@ -8283,12 +9633,12 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>부천</t>
+          <t>강원</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -8303,42 +9653,57 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>포항</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>울산</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="S91" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T91" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
         </is>
       </c>
     </row>
@@ -8370,50 +9735,77 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>대전</t>
+          <t>안양</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>부천</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="inlineStr"/>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>포항</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="S92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T92" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -8445,50 +9837,77 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>안양</t>
+          <t>대전</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>포항</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr"/>
-      <c r="M93" s="2" t="inlineStr"/>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>부천</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="S93" s="2" t="inlineStr">
+        <is>
+          <t>0.5/1</t>
+        </is>
+      </c>
+      <c r="T93" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -8525,45 +9944,72 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
           <t>강원</t>
         </is>
       </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr"/>
-      <c r="M94" s="2" t="inlineStr"/>
-      <c r="N94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="S94" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T94" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
         </is>
       </c>
     </row>
@@ -8595,50 +10041,77 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>광주</t>
+          <t>김천</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>울산</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr"/>
-      <c r="M95" s="2" t="inlineStr"/>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2/2.5</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
         </is>
       </c>
     </row>
@@ -8670,50 +10143,77 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>김천</t>
+          <t>광주</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>제주</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="2" t="inlineStr"/>
-      <c r="N96" s="2" t="inlineStr"/>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="S96" s="2" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+      <c r="T96" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -8755,40 +10255,1243 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
           <t>인천</t>
         </is>
       </c>
-      <c r="K97" s="2" t="inlineStr">
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="S97" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T97" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>07.11</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>김천</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>부천</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>07.11</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>광주</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>포항</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
+          <t>-0.5/1</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>07.11</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="S100" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>07.12</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="L97" s="2" t="inlineStr"/>
-      <c r="M97" s="2" t="inlineStr"/>
-      <c r="N97" s="2" t="inlineStr"/>
-      <c r="O97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>안양</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="S101" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T101" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>07.12</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="S102" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T102" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>07.12</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T103" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>07.18</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>07.18</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>김천</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T105" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>07.18</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>07.18</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>포항</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="S107" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T107" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>07.19</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>안양</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>광주</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>0.5/1</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>07.19</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>부천</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr"/>
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="S109" s="2" t="inlineStr">
+        <is>
+          <t>-0.5/1</t>
+        </is>
+      </c>
+      <c r="T109" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
         </is>
       </c>
     </row>

--- a/K리그 1_2026.xlsx
+++ b/K리그 1_2026.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T109"/>
+  <dimension ref="A1:T139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10964,11 +10964,19 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H104" s="2" t="inlineStr"/>
-      <c r="I104" s="2" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
           <t>5</t>
@@ -11058,11 +11066,19 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H105" s="2" t="inlineStr"/>
-      <c r="I105" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
           <t>11</t>
@@ -11155,11 +11171,19 @@
           <t>7</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr"/>
-      <c r="I106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -11249,8 +11273,16 @@
           <t>8</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr"/>
-      <c r="I107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -11343,8 +11375,16 @@
           <t>6</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
           <t>12</t>
@@ -11434,64 +11474,3076 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="R109" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="S109" s="2" t="inlineStr">
+        <is>
+          <t>-0.5/1</t>
+        </is>
+      </c>
+      <c r="T109" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>07.21</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="S110" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T110" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>07.21</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr">
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="S111" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T111" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>07.21</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K109" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="R112" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S112" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T112" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>07.22</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>부천</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>안양</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="S113" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T113" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>07.22</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>광주</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>김천</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="R114" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="S114" s="2" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T114" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>07.22</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>서울</t>
         </is>
       </c>
-      <c r="L109" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>포항</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
         <is>
           <t>4.50</t>
         </is>
       </c>
-      <c r="M109" s="2" t="inlineStr">
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R115" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S115" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T115" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>07.25</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>김천</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R116" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="S116" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T116" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>07.25</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>포항</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="R117" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="S117" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T117" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>07.26</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>안양</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="P118" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="R118" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S118" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T118" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>07.26</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>광주</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q119" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R119" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="S119" s="2" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T119" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>07.26</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>부천</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
         <is>
           <t>3.40</t>
         </is>
       </c>
-      <c r="N109" s="2" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="O109" s="2" t="inlineStr">
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="R120" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="S120" s="2" t="inlineStr">
+        <is>
+          <t>0.5/1</t>
+        </is>
+      </c>
+      <c r="T120" s="2" t="inlineStr">
         <is>
           <t>1.88</t>
         </is>
       </c>
-      <c r="P109" s="2" t="inlineStr">
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>07.26</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="R121" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="S121" s="2" t="inlineStr">
+        <is>
+          <t>0.5/1</t>
+        </is>
+      </c>
+      <c r="T121" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>08.01</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>부천</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr">
         <is>
           <t>2/2.5</t>
         </is>
       </c>
-      <c r="Q109" s="2" t="inlineStr">
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="S122" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T122" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>08.01</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S123" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T123" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>08.01</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>포항</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>김천</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
         <is>
           <t>1.93</t>
         </is>
       </c>
-      <c r="R109" s="2" t="inlineStr">
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="S124" s="2" t="inlineStr">
+        <is>
+          <t>0/0.5</t>
+        </is>
+      </c>
+      <c r="T124" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>08.02</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>광주</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="S109" s="2" t="inlineStr">
-        <is>
-          <t>-0.5/1</t>
-        </is>
-      </c>
-      <c r="T109" s="2" t="inlineStr">
+      <c r="S125" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T125" s="2" t="inlineStr">
         <is>
           <t>1.98</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>08.02</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="S126" s="2" t="inlineStr">
+        <is>
+          <t>0/-0.5</t>
+        </is>
+      </c>
+      <c r="T126" s="2" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>08.02</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>안양</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="R127" s="2" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="S127" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T127" s="2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>08.08</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>안양</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="R128" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="S128" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T128" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>08.08</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>부천</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>광주</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="R129" s="2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="S129" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T129" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>08.08</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>김천</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="S130" s="2" t="inlineStr">
+        <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="T130" s="2" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>08.08</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>2/2.5</t>
+        </is>
+      </c>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="R131" s="2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="S131" s="2" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>08.08</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>포항</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>09.27</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr"/>
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>08.15</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>광주</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr"/>
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>포항</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>08.15</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>제주</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr"/>
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>안양</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>08.15</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr"/>
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>대전</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>08.16</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>부천</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr"/>
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>전북</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>08.16</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>인천</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>김천</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>K리그 1</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>08.16</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>울산</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr"/>
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>강원</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
